--- a/diseases/d039/2000-2004.xlsx
+++ b/diseases/d039/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2084,9 +2078,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2628,9 +2619,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3403,9 +3391,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3947,9 +3932,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4722,9 +4704,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5266,9 +5245,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -6041,9 +6017,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6585,9 +6558,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -7360,9 +7330,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7904,9 +7871,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8679,9 +8643,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9223,9 +9184,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9998,9 +9956,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10542,9 +10497,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11317,9 +11269,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11861,9 +11810,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -12636,9 +12582,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -13180,9 +13123,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13955,9 +13895,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14499,9 +14436,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -15274,9 +15208,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15818,9 +15749,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16593,9 +16521,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -17137,9 +17062,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17681,9 +17603,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18308,9 +18227,6 @@
       <c r="O95" t="n">
         <v>151</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.3209797372931774</v>
       </c>
@@ -18456,9 +18372,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19000,9 +18913,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -19775,9 +19685,6 @@
       <c r="O103" t="n">
         <v>60</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.1275416174674877</v>
       </c>
@@ -19923,9 +19830,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -20467,9 +20371,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -21242,9 +21143,6 @@
       <c r="O111" t="n">
         <v>136</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.2890943329263055</v>
       </c>
@@ -21390,9 +21288,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21934,9 +21829,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22709,9 +22601,6 @@
       <c r="O119" t="n">
         <v>202</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.429390112140542</v>
       </c>
@@ -22857,9 +22746,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -23401,9 +23287,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -24176,9 +24059,6 @@
       <c r="O127" t="n">
         <v>329</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.6993532024467244</v>
       </c>
@@ -24324,9 +24204,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24868,9 +24745,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -25643,9 +25517,6 @@
       <c r="O135" t="n">
         <v>257</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.5463032614857392</v>
       </c>
@@ -25791,9 +25662,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -26335,9 +26203,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -27110,9 +26975,6 @@
       <c r="O143" t="n">
         <v>144</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.3060998819219706</v>
       </c>
@@ -27258,9 +27120,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -27802,9 +27661,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -28577,9 +28433,6 @@
       <c r="O151" t="n">
         <v>72</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.1530499409609853</v>
       </c>
@@ -28725,9 +28578,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -29269,9 +29119,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -30044,9 +29891,6 @@
       <c r="O159" t="n">
         <v>91</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.1934381198256897</v>
       </c>
@@ -30192,9 +30036,6 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -30736,9 +30577,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -31511,9 +31349,6 @@
       <c r="O167" t="n">
         <v>99</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.2104436688213547</v>
       </c>
@@ -31659,9 +31494,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -32203,9 +32035,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -32978,9 +32807,6 @@
       <c r="O175" t="n">
         <v>69</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.1466728600876109</v>
       </c>
@@ -33126,9 +32952,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -33670,9 +33493,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -34445,9 +34265,6 @@
       <c r="O183" t="n">
         <v>58</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.1232902302185715</v>
       </c>
@@ -34593,9 +34410,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -35137,9 +34951,6 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -35681,9 +35492,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -36077,9 +35885,6 @@
       <c r="O192" t="n">
         <v>28</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.05919771806327773</v>
       </c>
@@ -36225,9 +36030,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -36769,9 +36571,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -37313,9 +37112,6 @@
       <c r="O199" t="n">
         <v>22</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.04651249276400393</v>
       </c>
@@ -37461,9 +37257,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -38005,9 +37798,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -38549,9 +38339,6 @@
       <c r="O206" t="n">
         <v>41</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.08668237287837097</v>
       </c>
@@ -38697,9 +38484,6 @@
       <c r="O207" t="n">
         <v>2</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -39241,9 +39025,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -39785,9 +39566,6 @@
       <c r="O213" t="n">
         <v>113</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.2389050764696565</v>
       </c>
@@ -39933,9 +39711,6 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -40477,9 +40252,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -41021,9 +40793,6 @@
       <c r="O220" t="n">
         <v>114</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.2410192806862022</v>
       </c>
@@ -41169,9 +40938,6 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -41713,9 +41479,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -42257,9 +42020,6 @@
       <c r="O227" t="n">
         <v>127</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.2685039355012954</v>
       </c>
@@ -42405,9 +42165,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -42949,9 +42706,6 @@
       <c r="O231" t="n">
         <v>2</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -43493,9 +43247,6 @@
       <c r="O234" t="n">
         <v>95</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.2008494005718351</v>
       </c>
@@ -43641,9 +43392,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -44185,9 +43933,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -44729,9 +44474,6 @@
       <c r="O241" t="n">
         <v>57</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.1205096403431011</v>
       </c>
@@ -44877,9 +44619,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -45421,9 +45160,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -45965,9 +45701,6 @@
       <c r="O248" t="n">
         <v>45</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.09513918974455349</v>
       </c>
@@ -46113,9 +45846,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -46657,9 +46387,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -47201,9 +46928,6 @@
       <c r="O255" t="n">
         <v>47</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.09936759817764478</v>
       </c>
@@ -47349,9 +47073,6 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -47893,9 +47614,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -48437,9 +48155,6 @@
       <c r="O262" t="n">
         <v>47</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.09936759817764478</v>
       </c>
@@ -48585,9 +48300,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -49129,9 +48841,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -49673,9 +49382,6 @@
       <c r="O269" t="n">
         <v>28</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.05919771806327773</v>
       </c>
@@ -49821,9 +49527,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -50365,9 +50068,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -50909,9 +50609,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -51305,9 +51002,6 @@
       <c r="O278" t="n">
         <v>28</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.05892980051704796</v>
       </c>
@@ -51453,9 +51147,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -51997,9 +51688,6 @@
       <c r="O282" t="n">
         <v>1</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -52541,9 +52229,6 @@
       <c r="O285" t="n">
         <v>27</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.05682516478429625</v>
       </c>
@@ -52689,9 +52374,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -53233,9 +52915,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -53777,9 +53456,6 @@
       <c r="O292" t="n">
         <v>57</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.1199642367668476</v>
       </c>
@@ -53925,9 +53601,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -54469,9 +54142,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -55013,9 +54683,6 @@
       <c r="O299" t="n">
         <v>186</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.3914622462918186</v>
       </c>
@@ -55161,9 +54828,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -55705,9 +55369,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -56249,9 +55910,6 @@
       <c r="O306" t="n">
         <v>160</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.3367417172402741</v>
       </c>
@@ -56397,9 +56055,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -56941,9 +56596,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -57485,9 +57137,6 @@
       <c r="O313" t="n">
         <v>198</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.4167178750848392</v>
       </c>
@@ -57633,9 +57282,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -58177,9 +57823,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -58721,9 +58364,6 @@
       <c r="O320" t="n">
         <v>198</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.4167178750848392</v>
       </c>
@@ -58869,9 +58509,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -59413,9 +59050,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -59957,9 +59591,6 @@
       <c r="O327" t="n">
         <v>91</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.1915218516804059</v>
       </c>
@@ -60105,9 +59736,6 @@
       <c r="O328" t="n">
         <v>0</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0</v>
       </c>
@@ -60649,9 +60277,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -61193,9 +60818,6 @@
       <c r="O334" t="n">
         <v>82</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.1725801300856405</v>
       </c>
@@ -61341,9 +60963,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -61885,9 +61504,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -62429,9 +62045,6 @@
       <c r="O341" t="n">
         <v>101</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.212568209007923</v>
       </c>
@@ -62577,9 +62190,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -63121,9 +62731,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -63665,9 +63272,6 @@
       <c r="O348" t="n">
         <v>136</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.2862304596542329</v>
       </c>
@@ -63813,9 +63417,6 @@
       <c r="O349" t="n">
         <v>1</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -64357,9 +63958,6 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
@@ -64901,9 +64499,6 @@
       <c r="O355" t="n">
         <v>254</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.534577476118935</v>
       </c>
@@ -65049,9 +64644,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -65593,9 +65185,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -66137,9 +65726,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -66533,9 +66119,6 @@
       <c r="O364" t="n">
         <v>87</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.1824011201693068</v>
       </c>
@@ -66681,9 +66264,6 @@
       <c r="O365" t="n">
         <v>1</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -67225,9 +66805,6 @@
       <c r="O368" t="n">
         <v>1</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -67769,9 +67346,6 @@
       <c r="O371" t="n">
         <v>54</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.1132144883809491</v>
       </c>
@@ -67917,9 +67491,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -68461,9 +68032,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -69005,9 +68573,6 @@
       <c r="O378" t="n">
         <v>96</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0.2012702015661317</v>
       </c>
@@ -69153,9 +68718,6 @@
       <c r="O379" t="n">
         <v>1</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -69697,9 +69259,6 @@
       <c r="O382" t="n">
         <v>0</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0</v>
       </c>
@@ -70241,9 +69800,6 @@
       <c r="O385" t="n">
         <v>125</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.2620705749559006</v>
       </c>
@@ -70389,9 +69945,6 @@
       <c r="O386" t="n">
         <v>1</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -70933,9 +70486,6 @@
       <c r="O389" t="n">
         <v>0</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0</v>
       </c>
@@ -71477,9 +71027,6 @@
       <c r="O392" t="n">
         <v>219</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.4591476473227379</v>
       </c>
@@ -71625,9 +71172,6 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0</v>
       </c>
@@ -72169,9 +71713,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -72713,9 +72254,6 @@
       <c r="O399" t="n">
         <v>276</v>
       </c>
-      <c r="Q399" t="n">
-        <v>0</v>
-      </c>
       <c r="R399" t="n">
         <v>0.5786518295026285</v>
       </c>
@@ -72861,9 +72399,6 @@
       <c r="O400" t="n">
         <v>1</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -73405,9 +72940,6 @@
       <c r="O403" t="n">
         <v>0</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0</v>
       </c>
@@ -73949,9 +73481,6 @@
       <c r="O406" t="n">
         <v>227</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.4759201641199155</v>
       </c>
@@ -74097,9 +73626,6 @@
       <c r="O407" t="n">
         <v>0</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0</v>
       </c>
@@ -74641,9 +74167,6 @@
       <c r="O410" t="n">
         <v>0</v>
       </c>
-      <c r="Q410" t="n">
-        <v>0</v>
-      </c>
       <c r="R410" t="n">
         <v>0</v>
       </c>
@@ -75185,9 +74708,6 @@
       <c r="O413" t="n">
         <v>92</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.1928839431675428</v>
       </c>
@@ -75333,9 +74853,6 @@
       <c r="O414" t="n">
         <v>0</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0</v>
       </c>
@@ -75877,9 +75394,6 @@
       <c r="O417" t="n">
         <v>0</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0</v>
       </c>
@@ -76421,9 +75935,6 @@
       <c r="O420" t="n">
         <v>104</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0.2180427183633093</v>
       </c>
@@ -76569,9 +76080,6 @@
       <c r="O421" t="n">
         <v>1</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -77113,9 +76621,6 @@
       <c r="O424" t="n">
         <v>0</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0</v>
       </c>
@@ -77657,9 +77162,6 @@
       <c r="O427" t="n">
         <v>151</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.3165812545467279</v>
       </c>
@@ -77805,9 +77307,6 @@
       <c r="O428" t="n">
         <v>0</v>
       </c>
-      <c r="Q428" t="n">
-        <v>0</v>
-      </c>
       <c r="R428" t="n">
         <v>0</v>
       </c>
@@ -78349,9 +77848,6 @@
       <c r="O431" t="n">
         <v>0</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0</v>
       </c>
@@ -78893,9 +78389,6 @@
       <c r="O434" t="n">
         <v>122</v>
       </c>
-      <c r="Q434" t="n">
-        <v>0</v>
-      </c>
       <c r="R434" t="n">
         <v>0.255780881156959</v>
       </c>
@@ -79041,9 +78534,6 @@
       <c r="O435" t="n">
         <v>1</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -79585,9 +79075,6 @@
       <c r="O438" t="n">
         <v>0</v>
       </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
       <c r="R438" t="n">
         <v>0</v>
       </c>
@@ -80129,9 +79616,6 @@
       <c r="O441" t="n">
         <v>191</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0.4004438385326161</v>
       </c>
@@ -80276,9 +79760,6 @@
       </c>
       <c r="O442" t="n">
         <v>1</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>0</v>
       </c>
       <c r="R442" t="n">
         <v>0.02177822471534499</v>
